--- a/kospi200.xlsx
+++ b/kospi200.xlsx
@@ -423,7 +423,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
@@ -485,32 +485,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1,490,000</t>
+          <t>1,533,000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>149,000</t>
+          <t>46,000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,896,123</t>
+          <t>3,526,252</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>5조 6,147억원</t>
+          <t>5조 3,768억원</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1,088조 4,336억원</t>
+          <t>1,119조 8,448억원</t>
         </is>
       </c>
     </row>
@@ -527,452 +527,452 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>242,500</t>
+          <t>230,000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20,500</t>
+          <t>--12,000</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16,766,306</t>
+          <t>19,198,409</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4조 76억원</t>
+          <t>4조 5,259억원</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1,417조 7,226억원</t>
+          <t>1,344조 6,441억원</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>009150</t>
+          <t>005935</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1,305,000</t>
+          <t>183,900</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>104,000</t>
+          <t>--6,200</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>899,895</t>
+          <t>6,831,086</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1조 1,628억원</t>
+          <t>1조 2,811억원</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>97조 4,753억원</t>
+          <t>147조 5,561억원</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>402340</t>
+          <t>009150</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>920,000</t>
+          <t>1,288,000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>--18,000</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>997,399</t>
+          <t>675,422</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8,940억원</t>
+          <t>8,538억원</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>121조 3,701억원</t>
+          <t>96조 2,055억원</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>402340</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>190,400</t>
+          <t>955,000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19,300</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4,420,231</t>
+          <t>663,080</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8,232억원</t>
+          <t>6,282억원</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>152조 7,715억원</t>
+          <t>125조 9,874억원</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>64,100</t>
+          <t>538,000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3,970,493</t>
+          <t>932,516</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2,535억원</t>
+          <t>5,013억원</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>12조 5,636억원</t>
+          <t>43조 3,550억원</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>034020</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>532,000</t>
+          <t>56,200</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>24,000</t>
+          <t>--5,200</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>436,646</t>
+          <t>6,342,033</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2,305억원</t>
+          <t>3,495억원</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>42조 8,715억원</t>
+          <t>35조 9,995억원</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>035420</t>
+          <t>047040</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>178,500</t>
+          <t>11,880</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4,200</t>
+          <t>--2,390</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>-16.75</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1,087,551</t>
+          <t>27,474,216</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1,974억원</t>
+          <t>3,214억원</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>27조 1,514억원</t>
+          <t>4조 8,813억원</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>329180</t>
+          <t>373220</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HD현대중공업</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>285,500</t>
+          <t>360,000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>--6,000</t>
+          <t>--29,500</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>598,522</t>
+          <t>695,432</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1,727억원</t>
+          <t>2,500억원</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29조 9,664억원</t>
+          <t>84조 2,400억원</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>011070</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>368,000</t>
+          <t>63,500</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>--6,500</t>
+          <t>--700</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>476,894</t>
+          <t>2,599,098</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1,714억원</t>
+          <t>1,652억원</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8조 7,095억원</t>
+          <t>12조 4,460억원</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>138,900</t>
+          <t>305,500</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11,200</t>
+          <t>9,500</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1,121,344</t>
+          <t>496,376</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1,513억원</t>
+          <t>1,467억원</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6조 8,640억원</t>
+          <t>62조 1,590억원</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>017900</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>154,100</t>
+          <t>9,230</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>1,240</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>15.52</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>961,150</t>
+          <t>13,562,164</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1,476억원</t>
+          <t>1,308억원</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>54조 6,574억원</t>
+          <t>5,348억원</t>
         </is>
       </c>
     </row>
@@ -989,74 +989,74 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>162,600</t>
+          <t>155,500</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5,100</t>
+          <t>--6,200</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>853,544</t>
+          <t>802,172</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1,381억원</t>
+          <t>1,238억원</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>26조 4,850억원</t>
+          <t>25조 3,286억원</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>373220</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>387,000</t>
+          <t>131,950</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4,500</t>
+          <t>--7,750</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>352,395</t>
+          <t>864,753</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1,370억원</t>
+          <t>1,137억원</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>90조 5,580억원</t>
+          <t>22조 3,065억원</t>
         </is>
       </c>
     </row>
@@ -1073,326 +1073,326 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>324,000</t>
+          <t>325,000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>500</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>419,685</t>
+          <t>332,778</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1,359억원</t>
+          <t>1,081억원</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>52조 5,423억원</t>
+          <t>52조 7,045억원</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>296,500</t>
+          <t>91,000</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>--4,500</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>403,186</t>
+          <t>1,150,353</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1,201억원</t>
+          <t>1,006억원</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>60조 3,278억원</t>
+          <t>10조 1,334억원</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>032830</t>
+          <t>000150</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>삼성생명</t>
+          <t>두산</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>276,000</t>
+          <t>951,000</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>--62,000</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>-6.12</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>428,460</t>
+          <t>105,491</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1,187억원</t>
+          <t>983억원</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>55조 2,000억원</t>
+          <t>13조 5,398억원</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>034730</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>542,000</t>
+          <t>155,500</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44,500</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>207,534</t>
+          <t>622,185</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1,124억원</t>
+          <t>961억원</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>39조 2,965억원</t>
+          <t>55조 1,539억원</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>055550</t>
+          <t>329180</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>신한지주</t>
+          <t>HD현대중공업</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>87,800</t>
+          <t>274,500</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>--11,000</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1,274,505</t>
+          <t>350,908</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1,120억원</t>
+          <t>961억원</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>41조 2,177억원</t>
+          <t>28조 8,119억원</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>064400</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>LG씨엔에스</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>139,900</t>
+          <t>77,700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>--1,300</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>737,809</t>
+          <t>1,177,233</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1,014억원</t>
+          <t>922억원</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>23조 6,505억원</t>
+          <t>7조 5,280억원</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>035420</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>125,100</t>
+          <t>174,200</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>--1,300</t>
+          <t>--3,800</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>810,636</t>
+          <t>516,899</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>990억원</t>
+          <t>899억원</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>14조 841억원</t>
+          <t>26조 4,974억원</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>000150</t>
+          <t>032830</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>두산</t>
+          <t>삼성생명</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1,015,000</t>
+          <t>274,500</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>--3,000</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>98,395</t>
+          <t>320,363</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>987억원</t>
+          <t>881억원</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>14조 4,510억원</t>
+          <t>54조 9,000억원</t>
         </is>
       </c>
     </row>
@@ -1409,956 +1409,956 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>787,000</t>
+          <t>763,000</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>--24,000</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>122,570</t>
+          <t>116,557</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>967억원</t>
+          <t>869억원</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>40조 5,804억원</t>
+          <t>39조 3,429억원</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>042700</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>61,800</t>
+          <t>196,800</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2,900</t>
+          <t>--6,700</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1,558,293</t>
+          <t>441,861</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>953억원</t>
+          <t>863억원</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>39조 5,867억원</t>
+          <t>18조 7,574억원</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>353200</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>78,100</t>
+          <t>135,900</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4,600</t>
+          <t>--2,100</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1,178,327</t>
+          <t>643,136</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>919억원</t>
+          <t>861억원</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>16조 7,751억원</t>
+          <t>6조 7,158억원</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>267260</t>
+          <t>011070</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HD현대일렉트릭</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>463,000</t>
+          <t>347,000</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>--21,000</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>200,530</t>
+          <t>221,637</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>917억원</t>
+          <t>768억원</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>16조 6,898억원</t>
+          <t>8조 2,125억원</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>064400</t>
+          <t>055550</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LG씨엔에스</t>
+          <t>신한지주</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>79,100</t>
+          <t>88,200</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1,170,109</t>
+          <t>843,157</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>917억원</t>
+          <t>739억원</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>7조 6,637억원</t>
+          <t>41조 4,055억원</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>042660</t>
+          <t>489790</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52,600</t>
+          <t>47,550</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>--400</t>
+          <t>7,350</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1,737,001</t>
+          <t>1,483,751</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>908억원</t>
+          <t>653억원</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>16조 1,173억원</t>
+          <t>2조 4,007억원</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>202,500</t>
+          <t>644,000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>11,100</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>438,846</t>
+          <t>95,320</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>883억원</t>
+          <t>612억원</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>19조 3,007억원</t>
+          <t>28조 7,530억원</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>298040</t>
+          <t>010120</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>LS ELECTRIC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1,998,000</t>
+          <t>159,300</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>84,000</t>
+          <t>--5,300</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>40,569</t>
+          <t>389,007</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>805억원</t>
+          <t>612억원</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>18조 6,304억원</t>
+          <t>23조 8,950억원</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>068270</t>
+          <t>000270</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>190,300</t>
+          <t>109,700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1,700</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>405,830</t>
+          <t>563,177</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>777억원</t>
+          <t>602억원</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>44조 1,635억원</t>
+          <t>42조 8,283억원</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>003160</t>
+          <t>298040</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>디아이</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>44,150</t>
+          <t>1,924,000</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6,350</t>
+          <t>--74,000</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1,834,349</t>
+          <t>31,180</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>779억원</t>
+          <t>589억원</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1조 2,494억원</t>
+          <t>17조 9,404억원</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>034730</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>352,500</t>
+          <t>536,000</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>--4,000</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>216,276</t>
+          <t>104,439</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>759억원</t>
+          <t>563억원</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>31조 6,618억원</t>
+          <t>38조 8,614억원</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>115,700</t>
+          <t>16,000</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>--510</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>616,134</t>
+          <t>3,486,147</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>714억원</t>
+          <t>555억원</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>31조 3,512억원</t>
+          <t>14조 800억원</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>14,250</t>
+          <t>118,200</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>--200</t>
+          <t>2,900</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4,809,297</t>
+          <t>468,155</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>688억원</t>
+          <t>547억원</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5조 8,551억원</t>
+          <t>32조 286억원</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>071970</t>
+          <t>267260</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HD현대마린엔진</t>
+          <t>HD현대일렉트릭</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>40,850</t>
+          <t>443,000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5,300</t>
+          <t>--19,500</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1,629,063</t>
+          <t>123,689</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>679억원</t>
+          <t>544억원</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1조 3,857억원</t>
+          <t>15조 9,689억원</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>207940</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1,373,000</t>
+          <t>206,500</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>--1,000</t>
+          <t>--16,000</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-7.19</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>48,970</t>
+          <t>262,532</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>672억원</t>
+          <t>545억원</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>63조 5,575억원</t>
+          <t>15조 9,785억원</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>051910</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>LG화학</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>16,510</t>
+          <t>235,000</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>--1,000</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4,083,537</t>
+          <t>232,885</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>673억원</t>
+          <t>542억원</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>14조 5,288억원</t>
+          <t>16조 5,892억원</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>010120</t>
+          <t>068270</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LS ELECTRIC</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>164,700</t>
+          <t>188,700</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6,600</t>
+          <t>--1,100</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>400,068</t>
+          <t>264,664</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>654억원</t>
+          <t>502억원</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>24조 7,050억원</t>
+          <t>43조 7,922억원</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>003160</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>디아이</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>80,200</t>
+          <t>44,050</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>750</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>821,267</t>
+          <t>1,121,878</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>652억원</t>
+          <t>492억원</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1조 9,234억원</t>
+          <t>1조 2,466억원</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>000270</t>
+          <t>079550</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>107,700</t>
+          <t>429,000</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>--20,000</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>537,096</t>
+          <t>109,232</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>580억원</t>
+          <t>468억원</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>42조 475억원</t>
+          <t>9조 4,380억원</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>001210</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>26,750</t>
+          <t>8,030</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2,152,302</t>
+          <t>5,137,260</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>575억원</t>
+          <t>445억원</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6조 159억원</t>
+          <t>1,022억원</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>007660</t>
+          <t>007810</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>이수페타시스</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>96,900</t>
+          <t>74,000</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>--6,300</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>-7.85</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>567,563</t>
+          <t>591,189</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>537억원</t>
+          <t>440억원</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>7조 1,134억원</t>
+          <t>1조 7,747억원</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>051910</t>
+          <t>012330</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LG화학</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>240,500</t>
+          <t>359,500</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>223,660</t>
+          <t>127,467</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>527억원</t>
+          <t>444억원</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>16조 9,775억원</t>
+          <t>32조 2,905억원</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>278470</t>
+          <t>128940</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>289,000</t>
+          <t>387,500</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>11,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>184,784</t>
+          <t>113,498</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>524억원</t>
+          <t>434억원</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>10조 8,196억원</t>
+          <t>4조 9,643억원</t>
         </is>
       </c>
     </row>
@@ -2375,788 +2375,788 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>168,400</t>
+          <t>157,400</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>--1,000</t>
+          <t>--10,600</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-6.31</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>308,808</t>
+          <t>268,840</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>524억원</t>
+          <t>430억원</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>7조 2,592억원</t>
+          <t>6조 7,850억원</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>009540</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HD한국조선해양</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>242,000</t>
+          <t>30,700</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>--4,500</t>
+          <t>800</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>213,462</t>
+          <t>1,408,624</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>523억원</t>
+          <t>425억원</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>17조 1,271억원</t>
+          <t>22조 6,193억원</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>010060</t>
+          <t>042660</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OCI홀딩스</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>181,100</t>
+          <t>50,900</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>--1,600</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>284,135</t>
+          <t>832,147</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>514억원</t>
+          <t>421억원</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3조 3,812억원</t>
+          <t>15조 5,964억원</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>001820</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>637,000</t>
+          <t>112,900</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>--3,000</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6.70</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>80,233</t>
+          <t>363,935</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>509억원</t>
+          <t>418억원</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>28조 4,404억원</t>
+          <t>1조 1,736억원</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>033780</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>KT&amp;G</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>66,400</t>
+          <t>191,200</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3,300</t>
+          <t>3,100</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>776,428</t>
+          <t>212,655</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>505억원</t>
+          <t>407억원</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>12조 5,442억원</t>
+          <t>19조 8,486억원</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>009830</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>115,700</t>
+          <t>26,350</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5,300</t>
+          <t>--350</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>394,439</t>
+          <t>1,527,548</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>453억원</t>
+          <t>396억원</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1조 2,027억원</t>
+          <t>5조 9,259억원</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>000720</t>
+          <t>207940</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>96,000</t>
+          <t>1,362,000</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>--10,000</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>468,877</t>
+          <t>28,494</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>447억원</t>
+          <t>389억원</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>10조 6,902억원</t>
+          <t>63조 483억원</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>009540</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>HD한국조선해양</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>5,680</t>
+          <t>234,000</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>--170</t>
+          <t>--7,500</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>7,617,538</t>
+          <t>154,545</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>436억원</t>
+          <t>358억원</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>3조 364억원</t>
+          <t>16조 5,609억원</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>003670</t>
+          <t>007660</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>이수페타시스</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>168,600</t>
+          <t>92,800</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8,100</t>
+          <t>--4,000</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>247,755</t>
+          <t>383,958</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>419억원</t>
+          <t>356억원</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>14조 9,963억원</t>
+          <t>6조 8,124억원</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>128940</t>
+          <t>005490</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>POSCO홀딩스</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>369,500</t>
+          <t>277,000</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>--5,000</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>109,828</t>
+          <t>128,699</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>412억원</t>
+          <t>355억원</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4조 7,337억원</t>
+          <t>21조 9,499억원</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>29,900</t>
+          <t>122,700</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>--2,900</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1,306,332</t>
+          <t>281,745</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>395억원</t>
+          <t>342억원</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>13조 2,457억원</t>
+          <t>13조 8,139억원</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>079550</t>
+          <t>272210</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LIG디펜스앤에어로스페이스</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>451,000</t>
+          <t>65,100</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>--1,100</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>87,390</t>
+          <t>522,129</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>394억원</t>
+          <t>339억원</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>9조 9,220억원</t>
+          <t>12조 2,987억원</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>003230</t>
+          <t>278470</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>삼양식품</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1,182,000</t>
+          <t>278,000</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>--11,000</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>33,721</t>
+          <t>114,449</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>394억원</t>
+          <t>322억원</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>8조 9,040억원</t>
+          <t>10조 4,078억원</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>010060</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>OCI홀딩스</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>222,500</t>
+          <t>175,700</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>--4,600</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>177,491</t>
+          <t>183,464</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>393억원</t>
+          <t>316억원</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>17조 2,166억원</t>
+          <t>3조 2,804억원</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>005490</t>
+          <t>002990</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>POSCO홀딩스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>282,000</t>
+          <t>8,940</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>--240</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>137,214</t>
+          <t>3,186,381</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>388억원</t>
+          <t>306억원</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>22조 3,461억원</t>
+          <t>3,331억원</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>003670</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>102,500</t>
+          <t>162,600</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3,800</t>
+          <t>--6,300</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>380,727</t>
+          <t>179,781</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>387억원</t>
+          <t>293억원</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>9조 9,912억원</t>
+          <t>14조 4,627억원</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>161390</t>
+          <t>011790</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>한국타이어앤테크놀로지</t>
+          <t>SKC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>57,000</t>
+          <t>73,800</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>--9,100</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>684,195</t>
+          <t>388,338</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>387억원</t>
+          <t>291억원</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>7조 609억원</t>
+          <t>3조 6,604억원</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>033780</t>
+          <t>003230</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KT&amp;G</t>
+          <t>삼양식품</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>188,100</t>
+          <t>1,140,000</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>--52,000</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>203,005</t>
+          <t>24,856</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>383억원</t>
+          <t>287억원</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>19조 5,267억원</t>
+          <t>8조 5,876억원</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>29,950</t>
+          <t>89,400</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>--6,800</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1,255,828</t>
+          <t>295,082</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>376억원</t>
+          <t>260억원</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>22조 668억원</t>
+          <t>3조 4,169억원</t>
         </is>
       </c>
     </row>
@@ -3173,74 +3173,74 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>99,700</t>
+          <t>98,400</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>--1,800</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>370,871</t>
+          <t>265,475</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>368억원</t>
+          <t>259억원</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>4조 3,374억원</t>
+          <t>4조 2,809억원</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>443060</t>
+          <t>064350</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HD현대마린솔루션</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>175,400</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>--1,300</t>
+          <t>--3,800</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>204,218</t>
+          <t>326,679</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>364억원</t>
+          <t>257억원</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>7조 8,638억원</t>
+          <t>8조 6,222억원</t>
         </is>
       </c>
     </row>
@@ -3257,1393 +3257,1393 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>145,100</t>
+          <t>141,100</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>--4,000</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>251,769</t>
+          <t>184,324</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>362억원</t>
+          <t>256억원</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>11조 4,619억원</t>
+          <t>11조 1,459억원</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>260,500</t>
+          <t>29,550</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>--3,000</t>
+          <t>--450</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>132,466</t>
+          <t>891,563</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>342억원</t>
+          <t>256억원</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2조 9,565억원</t>
+          <t>2조 5,289억원</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>010580</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>에스엠벡셀</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>3,475</t>
+          <t>76,500</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>--1,500</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>9,483,083</t>
+          <t>331,755</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>325억원</t>
+          <t>251억원</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>3,866억원</t>
+          <t>16조 4,314억원</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>015760</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>123,900</t>
+          <t>28,200</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>--450</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>263,051</t>
+          <t>867,209</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>323억원</t>
+          <t>245억원</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>20조 7,343억원</t>
+          <t>18조 1,034억원</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>267270</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HD건설기계</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>81,200</t>
+          <t>157,300</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>--6,800</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>393,033</t>
+          <t>154,130</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>321억원</t>
+          <t>241억원</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>3조 8,568억원</t>
+          <t>4조 8,201억원</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>89,000</t>
+          <t>26,350</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>4,800</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>359,781</t>
+          <t>915,012</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>320억원</t>
+          <t>240억원</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>3조 6,212억원</t>
+          <t>9조 7,026억원</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>035720</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>29,200</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>--600</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>365,007</t>
+          <t>779,717</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>311억원</t>
+          <t>228억원</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>9,520억원</t>
+          <t>12조 9,356억원</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>000500</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>26,250</t>
+          <t>241,500</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>--11,000</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1,178,916</t>
+          <t>90,531</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>309억원</t>
+          <t>219억원</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>9조 6,658억원</t>
+          <t>7조 1,913억원</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>003550</t>
+          <t>267270</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>HD건설기계</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>99,800</t>
+          <t>78,700</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>--2,200</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>305,990</t>
+          <t>280,563</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>306억원</t>
+          <t>218억원</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>15조 890억원</t>
+          <t>3조 7,380억원</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>164,200</t>
+          <t>84,900</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>--4,100</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>187,809</t>
+          <t>245,865</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>306억원</t>
+          <t>209억원</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>5조 316억원</t>
+          <t>3조 4,544억원</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>82,300</t>
+          <t>80,100</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2,800</t>
+          <t>--4,200</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>369,649</t>
+          <t>258,846</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>302억원</t>
+          <t>207억원</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>7조 6,453억원</t>
+          <t>8,971억원</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>064350</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>82,800</t>
+          <t>82,400</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>359,733</t>
+          <t>253,869</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>296억원</t>
+          <t>205억원</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>9조 370억원</t>
+          <t>7조 6,546억원</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>475150</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>28,600</t>
+          <t>37,000</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>--1,800</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1,012,410</t>
+          <t>540,814</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>289억원</t>
+          <t>199억원</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>18조 3,602억원</t>
+          <t>1조 2,605억원</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>003550</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9,200</t>
+          <t>98,600</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>--1,200</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>3,182,770</t>
+          <t>200,286</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>286억원</t>
+          <t>197억원</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4,827억원</t>
+          <t>14조 9,075억원</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>006800</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>26,300</t>
+          <t>31,150</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1,950</t>
+          <t>--1,950</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1,089,123</t>
+          <t>612,806</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>285억원</t>
+          <t>189억원</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>14조 2,815억원</t>
+          <t>2조 5,994억원</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>001440</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>253,000</t>
+          <t>21,350</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>22,500</t>
+          <t>--750</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>115,359</t>
+          <t>878,595</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>284억원</t>
+          <t>187억원</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>7조 5,337억원</t>
+          <t>4조 1,844억원</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>016360</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>82,400</t>
+          <t>129,500</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>340,789</t>
+          <t>143,570</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>281억원</t>
+          <t>184억원</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>7조 3,583억원</t>
+          <t>21조 6,715억원</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>307950</t>
+          <t>071970</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>현대오토에버</t>
+          <t>HD현대마린엔진</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>350,500</t>
+          <t>36,800</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>--3,900</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>-9.58</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>77,977</t>
+          <t>481,862</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>272억원</t>
+          <t>177억원</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>9조 6,121억원</t>
+          <t>1조 2,483억원</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>090430</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>아모레퍼시픽</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>7,850</t>
+          <t>125,400</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>900</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>3,368,083</t>
+          <t>143,764</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>269억원</t>
+          <t>178억원</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>991억원</t>
+          <t>7조 3,350억원</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>000100</t>
+          <t>071050</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>한국금융지주</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>77,900</t>
+          <t>159,700</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>--2,100</t>
+          <t>5,700</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>331,453</t>
+          <t>111,134</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>263억원</t>
+          <t>173억원</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>5조 7,347억원</t>
+          <t>8조 8,994억원</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>281820</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>케이씨텍</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>95,800</t>
+          <t>100,600</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>3,900</t>
+          <t>--2,100</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>264,503</t>
+          <t>171,257</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>251억원</t>
+          <t>170억원</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1조 8,967억원</t>
+          <t>9조 8,060억원</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>011200</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>22,150</t>
+          <t>213,500</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>--250</t>
+          <t>--8,500</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1,090,733</t>
+          <t>79,573</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>244억원</t>
+          <t>169억원</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>20조 8,927억원</t>
+          <t>6조 6,612억원</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>011790</t>
+          <t>000100</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SKC</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>83,400</t>
+          <t>73,800</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>--3,500</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>288,757</t>
+          <t>225,529</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>240억원</t>
+          <t>168억원</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>4조 1,365억원</t>
+          <t>5조 4,328억원</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>307950</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>현대오토에버</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>33,100</t>
+          <t>336,000</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>--14,000</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>691,132</t>
+          <t>50,345</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>231억원</t>
+          <t>165억원</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2조 7,621억원</t>
+          <t>9조 2,145억원</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>005387</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>현대차2우B</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>8,050</t>
+          <t>163,400</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>3,800</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2,879,234</t>
+          <t>104,283</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>229억원</t>
+          <t>165억원</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4,664억원</t>
+          <t>5조 5,976억원</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>016360</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>22,150</t>
+          <t>83,300</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1,030,551</t>
+          <t>191,136</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>227억원</t>
+          <t>157억원</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>4조 3,412억원</t>
+          <t>7조 4,387억원</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>047050</t>
+          <t>003780</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>포스코인터내셔널</t>
+          <t>진양산업</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>49,750</t>
+          <t>6,040</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>--100</t>
+          <t>420</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>433,850</t>
+          <t>2,557,994</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>217억원</t>
+          <t>156억원</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>8조 7,522억원</t>
+          <t>785억원</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>112610</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>씨에스윈드</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>222,000</t>
+          <t>38,400</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>--800</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>98,092</t>
+          <t>399,138</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>217억원</t>
+          <t>151억원</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>6조 9,264억원</t>
+          <t>1조 6,194억원</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>195870</t>
+          <t>084670</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>해성디에스</t>
+          <t>동양고속</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>52,900</t>
+          <t>32,300</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>8,250</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>18.48</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>412,560</t>
+          <t>448,673</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>215억원</t>
+          <t>149억원</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>8,993억원</t>
+          <t>935억원</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>454910</t>
+          <t>047050</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>두산로보틱스</t>
+          <t>포스코인터내셔널</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>61,100</t>
+          <t>48,900</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>4,500</t>
+          <t>--850</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>328,852</t>
+          <t>304,604</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>199억원</t>
+          <t>148억원</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>3조 9,605억원</t>
+          <t>8조 6,026억원</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>071050</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>한국금융지주</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>154,200</t>
+          <t>114,800</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>8,700</t>
+          <t>--2,700</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>128,492</t>
+          <t>129,141</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>198억원</t>
+          <t>148억원</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>8조 5,929억원</t>
+          <t>2조 7,099억원</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>090430</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>124,500</t>
+          <t>248,500</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>--12,000</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>156,837</t>
+          <t>58,610</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>197억원</t>
+          <t>148억원</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>7조 2,823억원</t>
+          <t>2조 8,204억원</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>086280</t>
+          <t>030200</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>현대글로비스</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>187,000</t>
+          <t>45,750</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>6,600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>102,940</t>
+          <t>322,698</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>193억원</t>
+          <t>147억원</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>14조 250억원</t>
+          <t>11조 5,300억원</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>112610</t>
+          <t>006800</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>씨에스윈드</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>39,450</t>
+          <t>26,200</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4653,328 +4653,328 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>473,001</t>
+          <t>567,999</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>188억원</t>
+          <t>146억원</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1조 6,637억원</t>
+          <t>14조 2,272억원</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>020150</t>
+          <t>443060</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>롯데에너지머티리얼즈</t>
+          <t>HD현대마린솔루션</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>45,050</t>
+          <t>166,700</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>--8,100</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>413,664</t>
+          <t>84,398</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>187억원</t>
+          <t>140억원</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2조 3,591억원</t>
+          <t>7조 4,737억원</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>13,220</t>
+          <t>58,200</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>--100</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1,393,125</t>
+          <t>241,198</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>185억원</t>
+          <t>137억원</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4조 564억원</t>
+          <t>2조 2,520억원</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>457190</t>
+          <t>011200</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>이수스페셜티케미컬</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>76,500</t>
+          <t>22,150</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>3,100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>230,322</t>
+          <t>606,857</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>175억원</t>
+          <t>134억원</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2조 3,117억원</t>
+          <t>20조 8,927억원</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>039490</t>
+          <t>454910</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>키움증권</t>
+          <t>두산로보틱스</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>231,000</t>
+          <t>57,900</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>--2,600</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>75,477</t>
+          <t>231,487</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>174억원</t>
+          <t>134억원</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>6조 587억원</t>
+          <t>3조 7,531억원</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>001510</t>
+          <t>457190</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>이수스페셜티케미컬</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2,040</t>
+          <t>73,700</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>--45</t>
+          <t>--2,500</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>8,824,650</t>
+          <t>180,618</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>174억원</t>
+          <t>133억원</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>4,718억원</t>
+          <t>2조 2,271억원</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>001040</t>
+          <t>086280</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CJ</t>
+          <t>현대글로비스</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>115,100</t>
+          <t>188,900</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>1,900</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>150,954</t>
+          <t>71,552</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>174억원</t>
+          <t>132억원</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>3조 3,583억원</t>
+          <t>14조 1,675억원</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>018880</t>
+          <t>020150</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>한온시스템</t>
+          <t>롯데에너지머티리얼즈</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>3,720</t>
+          <t>43,800</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>--1,250</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>4,534,401</t>
+          <t>302,865</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>170억원</t>
+          <t>130억원</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>3조 8,177억원</t>
+          <t>2조 2,936억원</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>336260</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4984,699 +4984,699 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>1,300</t>
+          <t>--1,050</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>569,651</t>
+          <t>425,920</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>169억원</t>
+          <t>126억원</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2조 5,674억원</t>
+          <t>1조 9,648억원</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>005940</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>23,950</t>
+          <t>13,380</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>160</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>691,744</t>
+          <t>931,619</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>165억원</t>
+          <t>124억원</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>8조 8,425억원</t>
+          <t>4조 1,055억원</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>281820</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>케이씨텍</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>38,650</t>
+          <t>96,100</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>421,346</t>
+          <t>127,644</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>164억원</t>
+          <t>122억원</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1조 3,167억원</t>
+          <t>1조 9,027억원</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>005830</t>
+          <t>195870</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DB손해보험</t>
+          <t>해성디에스</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>180,300</t>
+          <t>51,600</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>1,900</t>
+          <t>--1,900</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>90,661</t>
+          <t>234,261</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>164억원</t>
+          <t>120억원</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>11조 8,097억원</t>
+          <t>8,772억원</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>030200</t>
+          <t>005830</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>DB손해보험</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>45,450</t>
+          <t>181,300</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>353,483</t>
+          <t>65,035</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>161억원</t>
+          <t>118억원</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>11조 4,544억원</t>
+          <t>11조 8,752억원</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>7,620</t>
+          <t>43,000</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>950</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2,094,559</t>
+          <t>273,116</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>158억원</t>
+          <t>116억원</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>3조 8,100억원</t>
+          <t>3조 6,657억원</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>021240</t>
+          <t>024110</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>코웨이</t>
+          <t>기업은행</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>101,800</t>
+          <t>19,120</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>--1,400</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>147,392</t>
+          <t>601,587</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>150억원</t>
+          <t>114억원</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>7조 2,041억원</t>
+          <t>15조 2,468억원</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>42,050</t>
+          <t>13,180</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>--1,830</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-12.19</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>354,520</t>
+          <t>827,544</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>150억원</t>
+          <t>113억원</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>3조 5,847억원</t>
+          <t>2,987억원</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>088980</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>맥쿼리인프라</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>147,700</t>
+          <t>9,430</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>--100</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>101,236</t>
+          <t>1,190,835</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>149억원</t>
+          <t>112억원</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1조 8,503억원</t>
+          <t>4조 5,162억원</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>024110</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>기업은행</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>18,890</t>
+          <t>5,710</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>--10</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>777,438</t>
+          <t>1,984,231</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>147억원</t>
+          <t>113억원</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>15조 634억원</t>
+          <t>3조 524억원</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>005387</t>
+          <t>009155</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>현대차2우B</t>
+          <t>삼성전기우</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>159,600</t>
+          <t>446,500</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>--16,000</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>91,456</t>
+          <t>24,877</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>146억원</t>
+          <t>109억원</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>5조 4,674억원</t>
+          <t>1조 2,980억원</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>117,500</t>
+          <t>77,900</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>2,700</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>119,918</t>
+          <t>140,636</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>141억원</t>
+          <t>108억원</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2조 7,736억원</t>
+          <t>6조 1,006억원</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>180640</t>
+          <t>018880</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>한진칼</t>
+          <t>한온시스템</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>125,400</t>
+          <t>3,655</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>5,200</t>
+          <t>--55</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>108,037</t>
+          <t>3,005,192</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>134억원</t>
+          <t>108억원</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>8조 3,720억원</t>
+          <t>3조 7,509억원</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>036570</t>
+          <t>004170</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>신세계</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>201,000</t>
+          <t>248,500</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>--9,000</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>64,176</t>
+          <t>43,762</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>130억원</t>
+          <t>107억원</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>4조 3,303억원</t>
+          <t>2조 3,471억원</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>009155</t>
+          <t>008770</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>삼성전기우</t>
+          <t>호텔신라</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>461,500</t>
+          <t>34,700</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>55,500</t>
+          <t>--1,800</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>13.67</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>28,521</t>
+          <t>307,646</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>127억원</t>
+          <t>106억원</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>1조 3,416억원</t>
+          <t>1조 3,619억원</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>004170</t>
+          <t>077500</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>신세계</t>
+          <t>유니퀘스트</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>257,500</t>
+          <t>12,060</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>12,500</t>
+          <t>800</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>48,547</t>
+          <t>878,925</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>124억원</t>
+          <t>104억원</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2조 4,321억원</t>
+          <t>2,605억원</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>014680</t>
+          <t>039490</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>키움증권</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>218,500</t>
+          <t>234,000</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>14,500</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>57,632</t>
+          <t>44,661</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>123억원</t>
+          <t>103억원</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2조 3,585억원</t>
+          <t>6조 1,374억원</t>
         </is>
       </c>
     </row>
@@ -5693,956 +5693,956 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>10,600</t>
+          <t>10,240</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>--320</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1,163,178</t>
+          <t>940,694</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>123억원</t>
+          <t>97.1억원</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>1조 1,369억원</t>
+          <t>1조 983억원</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>010130</t>
+          <t>120110</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>고려아연</t>
+          <t>코오롱인더</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>890,000</t>
+          <t>39,450</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>--950</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>13,710</t>
+          <t>248,343</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>122억원</t>
+          <t>96.4억원</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>18조 5,769억원</t>
+          <t>1조 1,814억원</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>229640</t>
+          <t>259960</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>LS에코에너지</t>
+          <t>크래프톤</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>55,200</t>
+          <t>179,600</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>--1,300</t>
+          <t>--3,600</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>215,331</t>
+          <t>52,780</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>119억원</t>
+          <t>95억원</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1조 6,905억원</t>
+          <t>8조 2,465억원</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>004710</t>
+          <t>0126Z0</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>한솔테크닉스</t>
+          <t>삼성에피스홀딩스</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>9,220</t>
+          <t>304,500</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>--12,000</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>1,282,468</t>
+          <t>30,710</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>113억원</t>
+          <t>94.1억원</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>4,891억원</t>
+          <t>7조 5,769억원</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>323410</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>41,650</t>
+          <t>19,400</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>--130</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>262,964</t>
+          <t>470,542</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>112억원</t>
+          <t>90.8억원</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2조 8,485억원</t>
+          <t>9조 2,561억원</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>120110</t>
+          <t>021240</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>코오롱인더</t>
+          <t>코웨이</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>40,450</t>
+          <t>101,200</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>--400</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>275,413</t>
+          <t>89,020</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>111억원</t>
+          <t>90.5억원</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>1조 2,113억원</t>
+          <t>7조 1,617억원</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>036570</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>58,300</t>
+          <t>197,600</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>--3,400</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>190,711</t>
+          <t>45,548</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>111억원</t>
+          <t>90.4억원</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2조 2,558억원</t>
+          <t>4조 2,571억원</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>175330</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>JB금융지주</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>24,450</t>
+          <t>143,000</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>--4,700</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>446,175</t>
+          <t>62,890</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>110억원</t>
+          <t>90.2억원</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>4조 5,605억원</t>
+          <t>1조 7,914억원</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>002380</t>
+          <t>014680</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>KCC</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>397,000</t>
+          <t>214,000</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>--5,500</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>27,080</t>
+          <t>41,892</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>109억원</t>
+          <t>90.5억원</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>3조 4,114억원</t>
+          <t>2조 3,099억원</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>051900</t>
+          <t>161390</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>LG생활건강</t>
+          <t>한국타이어앤테크놀로지</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>259,000</t>
+          <t>56,600</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>--200</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>41,349</t>
+          <t>158,214</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>108억원</t>
+          <t>89.4억원</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>3조 8,787억원</t>
+          <t>7조 113억원</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>006110</t>
+          <t>001040</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>삼아알미늄</t>
+          <t>CJ</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>62,800</t>
+          <t>113,000</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>--2,000</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>163,657</t>
+          <t>78,112</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>105억원</t>
+          <t>87.7억원</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>9,498억원</t>
+          <t>3조 2,970억원</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>006110</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>삼아알미늄</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>52,600</t>
+          <t>60,700</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2,950</t>
+          <t>--2,400</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>199,599</t>
+          <t>141,467</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>104억원</t>
+          <t>87.6억원</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>1조 9,099억원</t>
+          <t>9,180억원</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>31,250</t>
+          <t>10,030</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>--440</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>333,035</t>
+          <t>858,498</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>103억원</t>
+          <t>86.5억원</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2조 467억원</t>
+          <t>7,865억원</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>005385</t>
+          <t>034220</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>현대차우</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>157,100</t>
+          <t>7,430</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>--190</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>63,669</t>
+          <t>1,156,095</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>101억원</t>
+          <t>85.8억원</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>3조 5,880억원</t>
+          <t>3조 7,150억원</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>271560</t>
+          <t>0220W0</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>오리온</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>111,500</t>
+          <t>7,830</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>89,396</t>
+          <t>1,061,544</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>100억원</t>
+          <t>82.6억원</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>4조 4,075억원</t>
+          <t>6,618억원</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>000650</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>천일고속</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>7,820</t>
+          <t>195,600</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>--5,400</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>1,244,032</t>
+          <t>40,779</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>98.2억원</t>
+          <t>81.3억원</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>3,033억원</t>
+          <t>2,796억원</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>005385</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>현대차우</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>10,460</t>
+          <t>161,600</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>3,600</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>948,071</t>
+          <t>52,132</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>97.6억원</t>
+          <t>81.7억원</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>8,202억원</t>
+          <t>3조 6,908억원</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>008930</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>96,400</t>
+          <t>42,350</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>4,800</t>
+          <t>900</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>101,467</t>
+          <t>193,819</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>97.5억원</t>
+          <t>79.8억원</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>3조 6,844억원</t>
+          <t>2조 8,964억원</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>139130</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>iM금융지주</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>9,190</t>
+          <t>15,430</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>--140</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>1,038,579</t>
+          <t>504,735</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>96.3억원</t>
+          <t>76.9억원</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>3,424억원</t>
+          <t>2조 4,435억원</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>012750</t>
+          <t>004310</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>에스원</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>95,100</t>
+          <t>6,760</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>--200</t>
+          <t>--120</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>100,322</t>
+          <t>1,059,603</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>95.5억원</t>
+          <t>74.4억원</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>3조 6,137억원</t>
+          <t>2,163억원</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>032640</t>
+          <t>051900</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>LG유플러스</t>
+          <t>LG생활건강</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>13,790</t>
+          <t>255,000</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>--4,000</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>674,061</t>
+          <t>28,977</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>94억원</t>
+          <t>73.9억원</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>5조 8,529억원</t>
+          <t>3조 8,188억원</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>030000</t>
+          <t>011690</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>제일기획</t>
+          <t>와이투솔루션</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>18,510</t>
+          <t>3,345</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>--500</t>
+          <t>--670</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-16.69</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>498,363</t>
+          <t>1,947,049</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>93.1억원</t>
+          <t>73.8억원</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2조 1,294억원</t>
+          <t>1,228억원</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>204320</t>
+          <t>051630</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>HL만도</t>
+          <t>진양화학</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>39,200</t>
+          <t>2,450</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>1,550</t>
+          <t>335</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>234,405</t>
+          <t>3,045,060</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>91.1억원</t>
+          <t>73.8억원</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>1조 8,407억원</t>
+          <t>519억원</t>
         </is>
       </c>
     </row>
@@ -6659,830 +6659,830 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>58,800</t>
+          <t>56,300</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2,300</t>
+          <t>--2,600</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>154,220</t>
+          <t>130,366</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>90.5억원</t>
+          <t>73.3억원</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2조 8,039억원</t>
+          <t>2조 6,847억원</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>308170</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>씨티알모빌리티</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>16,450</t>
+          <t>4,940</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1,005</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>536,516</t>
+          <t>1,498,675</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>90.4억원</t>
+          <t>72.1억원</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>6,604억원</t>
+          <t>425억원</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>323410</t>
+          <t>217590</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>티엠씨</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>19,430</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>--150</t>
+          <t>--650</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>457,491</t>
+          <t>633,214</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>89.9억원</t>
+          <t>71.3억원</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>9조 2,705억원</t>
+          <t>2,626억원</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>004370</t>
+          <t>229640</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>농심</t>
+          <t>LS에코에너지</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>389,500</t>
+          <t>53,200</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>--3,500</t>
+          <t>--1,500</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>22,825</t>
+          <t>133,774</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>88.9억원</t>
+          <t>70.1억원</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2조 3,692억원</t>
+          <t>1조 6,292억원</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>175330</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>JB금융지주</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>75,400</t>
+          <t>25,350</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>900</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>114,402</t>
+          <t>281,058</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>87.3억원</t>
+          <t>70.5억원</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>5조 9,048억원</t>
+          <t>4조 7,283억원</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>088980</t>
+          <t>204320</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>맥쿼리인프라</t>
+          <t>HL만도</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>9,550</t>
+          <t>38,750</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>--40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>894,756</t>
+          <t>168,970</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>85.4억원</t>
+          <t>64.3억원</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>4조 5,737억원</t>
+          <t>1조 8,196억원</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>0126Z0</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>삼성에피스홀딩스</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>319,500</t>
+          <t>82,000</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>--1,700</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>26,311</t>
+          <t>77,811</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>83.7억원</t>
+          <t>63.2억원</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>7조 9,501억원</t>
+          <t>2조 3,197억원</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>088350</t>
+          <t>002380</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>한화생명</t>
+          <t>KCC</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>4,115</t>
+          <t>396,500</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>--500</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2,009,815</t>
+          <t>15,743</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>83.3억원</t>
+          <t>62.1억원</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>3조 5,740억원</t>
+          <t>3조 4,071억원</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>259960</t>
+          <t>005940</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>크래프톤</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>183,200</t>
+          <t>24,200</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>44,389</t>
+          <t>254,837</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>82억원</t>
+          <t>60.9억원</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>8조 4,118억원</t>
+          <t>8조 9,348억원</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>26,650</t>
+          <t>37,400</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>--1,100</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>302,376</t>
+          <t>161,866</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>80.8억원</t>
+          <t>60.7억원</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>3조 5,563억원</t>
+          <t>1조 9,538억원</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>7,720</t>
+          <t>10,760</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>1,035,221</t>
+          <t>567,262</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>80.3억원</t>
+          <t>60.6억원</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>6,525억원</t>
+          <t>2,582억원</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>004370</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>농심</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>15,010</t>
+          <t>386,500</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>--290</t>
+          <t>--3,000</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>543,508</t>
+          <t>15,741</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>80.2억원</t>
+          <t>60.8억원</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>3,401억원</t>
+          <t>2조 3,509억원</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>003010</t>
+          <t>073240</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>혜인</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>5,190</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>911,571</t>
+          <t>1,134,486</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>79.4억원</t>
+          <t>58.4억원</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>1,131억원</t>
+          <t>1조 4,909억원</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>450080</t>
+          <t>010130</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>에코프로머티</t>
+          <t>고려아연</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>30,450</t>
+          <t>873,000</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>--18,000</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>251,699</t>
+          <t>6,661</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>76.7억원</t>
+          <t>57.7억원</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2조 1,563억원</t>
+          <t>18조 2,221억원</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>012030</t>
+          <t>010640</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>진양폴리</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2,540</t>
+          <t>2,665</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2,963,882</t>
+          <t>2,098,945</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>75.6억원</t>
+          <t>57.4억원</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>5,110억원</t>
+          <t>445억원</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>139130</t>
+          <t>004020</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>iM금융지주</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>15,150</t>
+          <t>26,350</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>--200</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>500,909</t>
+          <t>224,981</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>75.3억원</t>
+          <t>58.7억원</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2조 3,992억원</t>
+          <t>3조 5,163억원</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>077500</t>
+          <t>450080</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>유니퀘스트</t>
+          <t>에코프로머티</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>11,330</t>
+          <t>28,850</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>--530</t>
+          <t>--1,500</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>653,546</t>
+          <t>195,875</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>74.9억원</t>
+          <t>56.9억원</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2,447억원</t>
+          <t>2조 430억원</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>001510</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>SK증권</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>1,971</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>--850</t>
+          <t>--69</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>144,148</t>
+          <t>2,822,982</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>73.6억원</t>
+          <t>55.7억원</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>1조 5,841억원</t>
+          <t>4,559억원</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>217590</t>
+          <t>004710</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>티엠씨</t>
+          <t>한솔테크닉스</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>11,600</t>
+          <t>9,060</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>--160</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>593,468</t>
+          <t>624,709</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>69.3억원</t>
+          <t>56.1억원</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2,795억원</t>
+          <t>4,806억원</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>009900</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>38,500</t>
+          <t>8,460</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>--730</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>172,288</t>
+          <t>654,454</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>67.1억원</t>
+          <t>55.9억원</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2조 113억원</t>
+          <t>4,439억원</t>
         </is>
       </c>
     </row>
@@ -7499,32 +7499,32 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>169,800</t>
+          <t>171,100</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>1,100</t>
+          <t>1,300</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>38,641</t>
+          <t>30,866</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>65.7억원</t>
+          <t>52.5억원</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2조 5,562억원</t>
+          <t>2조 5,758억원</t>
         </is>
       </c>
     </row>
@@ -7541,74 +7541,74 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>17,100</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>--840</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>369,060</t>
+          <t>305,380</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>65.7억원</t>
+          <t>52.3억원</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>6,034억원</t>
+          <t>5,765억원</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>017800</t>
+          <t>013360</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>현대엘리베이터</t>
+          <t>일성건설</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>67,300</t>
+          <t>1,312</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>95,508</t>
+          <t>3,633,759</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>64.7억원</t>
+          <t>50.5억원</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2조 6,309억원</t>
+          <t>709억원</t>
         </is>
       </c>
     </row>
@@ -7625,1250 +7625,1250 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>31,200</t>
+          <t>30,300</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>--100</t>
+          <t>--900</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>198,398</t>
+          <t>161,174</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>62억원</t>
+          <t>48.8억원</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>1조 1,189억원</t>
+          <t>1조 866억원</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>036460</t>
+          <t>069960</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>한국가스공사</t>
+          <t>현대백화점</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>36,900</t>
+          <t>74,700</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>--1,100</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>165,638</t>
+          <t>63,141</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>61.2억원</t>
+          <t>46.9억원</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>3조 4,063억원</t>
+          <t>1조 6,109억원</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>192650</t>
+          <t>271560</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>드림텍</t>
+          <t>오리온</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>7,290</t>
+          <t>112,200</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>--220</t>
+          <t>700</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>804,866</t>
+          <t>41,095</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>60.3억원</t>
+          <t>46.1억원</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>4,803억원</t>
+          <t>4조 4,351억원</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>008770</t>
+          <t>180640</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>호텔신라</t>
+          <t>한진칼</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>36,650</t>
+          <t>123,100</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>1,150</t>
+          <t>--2,300</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>164,366</t>
+          <t>37,021</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>60.1억원</t>
+          <t>45.5억원</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>1조 4,384억원</t>
+          <t>8조 2,184억원</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>308170</t>
+          <t>051600</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>씨티알모빌리티</t>
+          <t>한전KPS</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>4,020</t>
+          <t>41,350</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>--200</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>1,367,028</t>
+          <t>109,867</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>59.8억원</t>
+          <t>44.8억원</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>346억원</t>
+          <t>1조 8,608억원</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>088350</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>126,000</t>
+          <t>4,095</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>--20</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>46,946</t>
+          <t>1,086,967</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>59.1억원</t>
+          <t>44.1억원</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2조 1,778억원</t>
+          <t>3조 5,566억원</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>017960</t>
+          <t>241560</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>한국카본</t>
+          <t>두산밥캣</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>15,790</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>--450</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>364,477</t>
+          <t>86,377</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>57억원</t>
+          <t>42억원</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>8,160억원</t>
+          <t>4조 6,969억원</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>069960</t>
+          <t>032640</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>현대백화점</t>
+          <t>LG유플러스</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>75,800</t>
+          <t>13,890</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>74,829</t>
+          <t>288,988</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>56.4억원</t>
+          <t>40.1억원</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>1조 6,346억원</t>
+          <t>5조 8,953억원</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>001780</t>
+          <t>017800</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>알루코</t>
+          <t>현대엘리베이터</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>1,625</t>
+          <t>67,100</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>--248</t>
+          <t>--200</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>3,308,107</t>
+          <t>58,967</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>56.4억원</t>
+          <t>39.3억원</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>1,573억원</t>
+          <t>2조 6,231억원</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>003780</t>
+          <t>030000</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>진양산업</t>
+          <t>제일기획</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>5,660</t>
+          <t>18,730</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>1,002,355</t>
+          <t>202,752</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>56.4억원</t>
+          <t>37.8억원</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>736억원</t>
+          <t>2조 1,547억원</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>294870</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>IPARK현대산업개발</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>83,700</t>
+          <t>24,950</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>67,089</t>
+          <t>152,406</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>56억원</t>
+          <t>37.7억원</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2조 3,678억원</t>
+          <t>1조 6,444억원</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>139480</t>
+          <t>017960</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>이마트</t>
+          <t>한국카본</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>68,500</t>
+          <t>15,650</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2,100</t>
+          <t>--140</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>80,775</t>
+          <t>242,189</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>55.1억원</t>
+          <t>37.4억원</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>1조 8,903억원</t>
+          <t>8,087억원</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>139480</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>이마트</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>5,190</t>
+          <t>69,100</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>700</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>1,038,906</t>
+          <t>51,982</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>53.7억원</t>
+          <t>35.8억원</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>1조 4,909억원</t>
+          <t>1조 9,069억원</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>097520</t>
+          <t>003010</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>엠씨넥스</t>
+          <t>혜인</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>19,970</t>
+          <t>8,150</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>--1,480</t>
+          <t>--670</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-7.60</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>257,057</t>
+          <t>437,994</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>52.8억원</t>
+          <t>35.7억원</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>3,475억원</t>
+          <t>1,036억원</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>241560</t>
+          <t>010580</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>두산밥캣</t>
+          <t>에스엠벡셀</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>49,450</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>--120</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>105,386</t>
+          <t>1,042,034</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>52.2억원</t>
+          <t>35.2억원</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>4조 7,401억원</t>
+          <t>3,771억원</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>011780</t>
+          <t>001120</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>금호석유화학</t>
+          <t>LX인터내셔널</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>106,800</t>
+          <t>39,950</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>--300</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>48,014</t>
+          <t>88,247</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>51억원</t>
+          <t>35.1억원</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2조 6,614억원</t>
+          <t>1조 5,485억원</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>001120</t>
+          <t>053690</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>LX인터내셔널</t>
+          <t>한미글로벌</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>40,250</t>
+          <t>17,060</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>--1,150</t>
+          <t>--1,160</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>121,629</t>
+          <t>206,553</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>49.1억원</t>
+          <t>34억원</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>1조 5,601억원</t>
+          <t>1,869억원</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>035250</t>
+          <t>111770</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>강원랜드</t>
+          <t>영원무역</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>13,680</t>
+          <t>68,100</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>--30</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>352,770</t>
+          <t>50,253</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>48.4억원</t>
+          <t>34.1억원</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2조 9,267억원</t>
+          <t>3조 176억원</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>084670</t>
+          <t>013580</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>동양고속</t>
+          <t>계룡건설</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>31,900</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>--1,950</t>
+          <t>--2,350</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>143,802</t>
+          <t>138,145</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>47억원</t>
+          <t>33.4억원</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>924억원</t>
+          <t>2,126억원</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>000815</t>
+          <t>251270</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>삼성화재우</t>
+          <t>넷마블</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>396,000</t>
+          <t>33,350</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>11,500</t>
+          <t>--200</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>11,617</t>
+          <t>96,582</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>45.6억원</t>
+          <t>32.1억원</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>1조 1,908억원</t>
+          <t>2조 7,733억원</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>066575</t>
+          <t>000880</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>LG전자우</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>60,200</t>
+          <t>91,900</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>3,400</t>
+          <t>--2,100</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>76,205</t>
+          <t>34,844</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>45.4억원</t>
+          <t>31.7억원</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>1조 343억원</t>
+          <t>4조 9,009억원</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>000155</t>
+          <t>00680K</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>두산우</t>
+          <t>미래에셋증권2우B</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>353,500</t>
+          <t>9,310</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>28,000</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>12,451</t>
+          <t>333,932</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>42.9억원</t>
+          <t>30.9억원</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>1조 2,133억원</t>
+          <t>1조 1,849억원</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>294870</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>IPARK현대산업개발</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>24,500</t>
+          <t>126,400</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>173,116</t>
+          <t>25,268</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>42.2억원</t>
+          <t>31.9억원</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>1조 6,147억원</t>
+          <t>2조 1,847억원</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>029780</t>
+          <t>035250</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>삼성카드</t>
+          <t>강원랜드</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>40,850</t>
+          <t>13,590</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>--90</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>102,101</t>
+          <t>224,189</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>41.9억원</t>
+          <t>30.5억원</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>4조 7,328억원</t>
+          <t>2조 9,075억원</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>10,230</t>
+          <t>47,300</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>--1,700</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>391,021</t>
+          <t>63,302</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>39.9억원</t>
+          <t>30억원</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>6,138억원</t>
+          <t>1조 5,292억원</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>383220</t>
+          <t>000155</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>F&amp;F</t>
+          <t>두산우</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>61,600</t>
+          <t>321,500</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>--32,000</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>64,560</t>
+          <t>9,257</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>39.8억원</t>
+          <t>29.7억원</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2조 3,597억원</t>
+          <t>1조 1,035억원</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>285130</t>
+          <t>025560</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SK케미칼</t>
+          <t>미래산업</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>41,650</t>
+          <t>8,060</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2,350</t>
+          <t>170</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>94,775</t>
+          <t>370,424</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>39.7억원</t>
+          <t>29.6억원</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>7,205억원</t>
+          <t>2,239억원</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>081660</t>
+          <t>192650</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>미스토홀딩스</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>36,350</t>
+          <t>7,060</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>--230</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>106,146</t>
+          <t>414,616</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>38.7억원</t>
+          <t>29.4억원</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>1조 9,299억원</t>
+          <t>4,652억원</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>000880</t>
+          <t>100090</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>SK오션플랜트</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>94,000</t>
+          <t>9,240</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>1,300</t>
+          <t>--360</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>40,869</t>
+          <t>317,224</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>38.6억원</t>
+          <t>29.2억원</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>5조 129억원</t>
+          <t>5,773억원</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>251270</t>
+          <t>011170</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>넷마블</t>
+          <t>롯데케미칼</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>33,550</t>
+          <t>47,150</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>--100</t>
+          <t>--750</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>111,813</t>
+          <t>61,936</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>37.9억원</t>
+          <t>28.9억원</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2조 7,900억원</t>
+          <t>2조 169억원</t>
         </is>
       </c>
     </row>
